--- a/results/llama3_2_latest__gatefix/comparison_SelfCorrectionRAG/SelfCorrectionRAG_consolidated.xlsx
+++ b/results/llama3_2_latest__gatefix/comparison_SelfCorrectionRAG/SelfCorrectionRAG_consolidated.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -545,44 +545,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.01010100960871342</v>
+        <v>0.1651376098416708</v>
       </c>
       <c r="D2" t="n">
-        <v>7.188271943170174e-260</v>
+        <v>0.01890362647341236</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3537169694900513</v>
+        <v>0.6061280369758606</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.694999999999993</v>
+        <v>11.17238372093027</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07379375591296121</v>
+        <v>0.8107852412488175</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
       <c r="K2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.2795698924731183</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="N2" t="n">
-        <v>7.416308641433716</v>
+        <v>98.44901013374329</v>
       </c>
       <c r="O2" t="n">
-        <v>1502.359375</v>
+        <v>196.09375</v>
       </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
@@ -591,10 +593,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.075171232223511</v>
+        <v>1.974961996078491</v>
       </c>
       <c r="T2" t="n">
-        <v>1.078155040740967</v>
+        <v>37.80867099761963</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -610,44 +612,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.0983606529965064</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>9.039352811507815e-232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4298741221427917</v>
+        <v>0.5689552426338196</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.694999999999993</v>
+        <v>33.14685897435899</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7155963302752294</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
       <c r="K3" t="n">
-        <v>0.38</v>
+        <v>0.045</v>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="N3" t="n">
-        <v>12.04212021827698</v>
+        <v>80.98165202140808</v>
       </c>
       <c r="O3" t="n">
-        <v>1502.90234375</v>
+        <v>139.234375</v>
       </c>
       <c r="P3" t="n">
-        <v>10.1</v>
+        <v>6.9</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
@@ -656,10 +660,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5174560546875</v>
+        <v>2.944238185882568</v>
       </c>
       <c r="T3" t="n">
-        <v>1.519016027450562</v>
+        <v>29.74052214622498</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -675,44 +679,46 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.2211538424038462</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1.734430471313534e-80</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2991204261779785</v>
+        <v>0.6441602110862732</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.694999999999993</v>
+        <v>54.93275</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.3472222222222222</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2045454545454545</v>
       </c>
       <c r="N4" t="n">
-        <v>11.06787991523743</v>
+        <v>80.6724648475647</v>
       </c>
       <c r="O4" t="n">
-        <v>1503.2890625</v>
+        <v>143.75</v>
       </c>
       <c r="P4" t="n">
-        <v>10.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q4" t="n">
         <v>4</v>
@@ -721,10 +727,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.499449968338013</v>
+        <v>2.559149026870728</v>
       </c>
       <c r="T4" t="n">
-        <v>1.501154899597168</v>
+        <v>40.09256076812744</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -740,19 +746,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.0517241367215369</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1.691240673366888e-244</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2943938076496124</v>
+        <v>0.406010240316391</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.694999999999993</v>
+        <v>18.74250000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06382978723404255</v>
+        <v>0.1178396072013093</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -760,36 +766,38 @@
       <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="N5" t="n">
-        <v>11.57150030136108</v>
+        <v>32.07939291000366</v>
       </c>
       <c r="O5" t="n">
-        <v>1503.33984375</v>
+        <v>144.421875</v>
       </c>
       <c r="P5" t="n">
-        <v>9.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.538486480712891</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.54012393951416</v>
+        <v>32.07938885688782</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -805,19 +813,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01273885288652687</v>
+        <v>0.09523809351473926</v>
       </c>
       <c r="D6" t="n">
-        <v>7.842246496009318e-255</v>
+        <v>1.724007354605445e-238</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3298570215702057</v>
+        <v>0.4076820313930511</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.694999999999993</v>
+        <v>40.09</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0896551724137931</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -825,36 +833,38 @@
       <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="N6" t="n">
-        <v>11.0548632144928</v>
+        <v>36.28087973594666</v>
       </c>
       <c r="O6" t="n">
-        <v>1503.58203125</v>
+        <v>143.171875</v>
       </c>
       <c r="P6" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.51356315612793</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.515053033828735</v>
+        <v>36.28086876869202</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -870,56 +880,58 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.004032257864935623</v>
+        <v>0.1007462671185815</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3.015350835165496e-79</v>
       </c>
       <c r="E7" t="n">
-        <v>0.353213906288147</v>
+        <v>0.5569169521331787</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.694999999999993</v>
+        <v>11.85032253947148</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02269421006691882</v>
+        <v>0.2173407041024149</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2</v>
+        <v>0.4560943643512451</v>
       </c>
       <c r="N7" t="n">
-        <v>13.68193173408508</v>
+        <v>1985.307137012482</v>
       </c>
       <c r="O7" t="n">
-        <v>1504.91796875</v>
+        <v>37.265625</v>
       </c>
       <c r="P7" t="n">
-        <v>10.4</v>
+        <v>6.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.481336832046509</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.48303484916687</v>
+        <v>1985.307085037231</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -935,56 +947,58 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.08835341211012726</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2.796173118931514e-164</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3415371477603912</v>
+        <v>0.5113056302070618</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.694999999999993</v>
+        <v>47.43431818181818</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05416666666666667</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="N8" t="n">
-        <v>10.56893277168274</v>
+        <v>102.6565487384796</v>
       </c>
       <c r="O8" t="n">
-        <v>1504.91796875</v>
+        <v>32.484375</v>
       </c>
       <c r="P8" t="n">
-        <v>8.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.484270572662354</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.48605489730835</v>
+        <v>102.6565148830414</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1000,19 +1014,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.006993006649469429</v>
+        <v>0.1609907098118452</v>
       </c>
       <c r="D9" t="n">
-        <v>4.626996437597695e-283</v>
+        <v>1.050480840321343e-159</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3237474858760834</v>
+        <v>0.6321372389793396</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.694999999999993</v>
+        <v>76.27844155844159</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04519119351100811</v>
+        <v>0.1622247972190035</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1020,24 +1034,26 @@
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" t="n">
         <v>0.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="N9" t="n">
-        <v>4.290479421615601</v>
+        <v>175.2775340080261</v>
       </c>
       <c r="O9" t="n">
-        <v>1504.91796875</v>
+        <v>106.609375</v>
       </c>
       <c r="P9" t="n">
-        <v>12.5</v>
+        <v>6.3</v>
       </c>
       <c r="Q9" t="n">
         <v>4</v>
@@ -1046,10 +1062,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.485265493392944</v>
+        <v>4.023576974868774</v>
       </c>
       <c r="T9" t="n">
-        <v>1.486840009689331</v>
+        <v>105.5454730987549</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1065,44 +1081,46 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.1533333300935556</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.0009558604485990607</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3335631489753723</v>
+        <v>0.5622940063476562</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.694999999999993</v>
+        <v>55.06017657192078</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05158730158730158</v>
+        <v>0.2645502645502645</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0.25</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="N10" t="n">
-        <v>2.373820304870605</v>
+        <v>155.859249830246</v>
       </c>
       <c r="O10" t="n">
-        <v>1504.91796875</v>
+        <v>41.890625</v>
       </c>
       <c r="P10" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
         <v>4</v>
@@ -1111,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4668910503387451</v>
+        <v>2.421268939971924</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4685661792755127</v>
+        <v>77.42440891265869</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1130,44 +1148,46 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.006756756424625656</v>
+        <v>0.1137724528464628</v>
       </c>
       <c r="D11" t="n">
-        <v>3.199290466293744e-295</v>
+        <v>4.817247629422568e-161</v>
       </c>
       <c r="E11" t="n">
-        <v>0.312595933675766</v>
+        <v>0.6700990796089172</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.694999999999993</v>
+        <v>51.24500000000003</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04264625478403499</v>
+        <v>0.1623838162930563</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2</v>
       </c>
       <c r="N11" t="n">
-        <v>12.0915265083313</v>
+        <v>130.7491688728333</v>
       </c>
       <c r="O11" t="n">
-        <v>1504.91796875</v>
+        <v>38.03125</v>
       </c>
       <c r="P11" t="n">
-        <v>10.9</v>
+        <v>7.2</v>
       </c>
       <c r="Q11" t="n">
         <v>4</v>
@@ -1176,10 +1196,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.399059534072876</v>
+        <v>3.031794309616089</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4006154537200928</v>
+        <v>63.4993622303009</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1195,19 +1215,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.1230769207358107</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1.968548384043637e-159</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3295387625694275</v>
+        <v>0.5097022652626038</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.694999999999993</v>
+        <v>64.28885057471265</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04441913439635535</v>
+        <v>0.1503416856492027</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1215,36 +1235,38 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="N12" t="n">
-        <v>10.56877565383911</v>
+        <v>93.94772005081177</v>
       </c>
       <c r="O12" t="n">
-        <v>1504.921875</v>
+        <v>26.484375</v>
       </c>
       <c r="P12" t="n">
-        <v>9.6</v>
+        <v>11.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.455920219421387</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.457530975341797</v>
+        <v>93.94767928123474</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1260,44 +1282,46 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.006644517945718055</v>
+        <v>0.08668730496947161</v>
       </c>
       <c r="D13" t="n">
-        <v>1.737745674680046e-291</v>
+        <v>2.573767504571472e-165</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3309608399868011</v>
+        <v>0.6250803470611572</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.694999999999993</v>
+        <v>72.83000000000003</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04323725055432372</v>
+        <v>0.1036585365853658</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.12</v>
       </c>
       <c r="N13" t="n">
-        <v>11.13385796546936</v>
+        <v>156.8315689563751</v>
       </c>
       <c r="O13" t="n">
-        <v>1505.24609375</v>
+        <v>39.625</v>
       </c>
       <c r="P13" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="Q13" t="n">
         <v>4</v>
@@ -1306,10 +1330,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.483949184417725</v>
+        <v>3.926463842391968</v>
       </c>
       <c r="T13" t="n">
-        <v>1.485470056533813</v>
+        <v>85.08348488807678</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1325,44 +1349,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.1144578291152563</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>5.033313304015413e-160</v>
       </c>
       <c r="E14" t="n">
-        <v>0.327696293592453</v>
+        <v>0.5496810078620911</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.694999999999993</v>
+        <v>59.57166666666666</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04333333333333333</v>
+        <v>0.1538888888888889</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
       <c r="K14" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.25</v>
+        <v>0.4411764705882353</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="N14" t="n">
-        <v>10.40467143058777</v>
+        <v>139.3563277721405</v>
       </c>
       <c r="O14" t="n">
-        <v>1505.5625</v>
+        <v>39.46875</v>
       </c>
       <c r="P14" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="Q14" t="n">
         <v>4</v>
@@ -1371,10 +1397,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.564459562301636</v>
+        <v>2.741819143295288</v>
       </c>
       <c r="T14" t="n">
-        <v>1.566574096679688</v>
+        <v>66.50416898727417</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1390,44 +1416,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.2658227801634354</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2.778062000719693e-155</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3345783352851868</v>
+        <v>0.6809143424034119</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.694999999999993</v>
+        <v>58.71729813664598</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1569416498993964</v>
+        <v>0.7183098591549296</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.25</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="M15" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="N15" t="n">
-        <v>4.041972637176514</v>
+        <v>113.7983701229095</v>
       </c>
       <c r="O15" t="n">
-        <v>1505.5625</v>
+        <v>85.421875</v>
       </c>
       <c r="P15" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
         <v>4</v>
@@ -1436,10 +1464,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.564634799957275</v>
+        <v>2.529568910598755</v>
       </c>
       <c r="T15" t="n">
-        <v>2.566180944442749</v>
+        <v>54.16732096672058</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1455,56 +1483,58 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.2511627858976745</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.08135740764894293</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3279084861278534</v>
+        <v>0.6782683730125427</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.694999999999993</v>
+        <v>67.17797468354433</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1112696148359486</v>
+        <v>0.8473609129814551</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.349112426035503</v>
       </c>
       <c r="N16" t="n">
-        <v>2.722403526306152</v>
+        <v>105.8721721172333</v>
       </c>
       <c r="O16" t="n">
-        <v>1505.56640625</v>
+        <v>36.25</v>
       </c>
       <c r="P16" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.453002691268921</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.454621553421021</v>
+        <v>105.8721449375153</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1520,44 +1550,46 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.276923072662722</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>8.87895296788668e-156</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3277542293071747</v>
+        <v>0.6541492938995361</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.694999999999993</v>
+        <v>61.6818376623377</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1048387096774194</v>
+        <v>0.4973118279569892</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0.25</v>
+        <v>0.3877551020408163</v>
       </c>
       <c r="M17" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="N17" t="n">
-        <v>1.138053894042969</v>
+        <v>149.7484121322632</v>
       </c>
       <c r="O17" t="n">
-        <v>1506.00390625</v>
+        <v>23.03125</v>
       </c>
       <c r="P17" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
@@ -1566,10 +1598,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3933370113372803</v>
+        <v>3.591459989547729</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3949875831604004</v>
+        <v>93.34073901176453</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1585,56 +1617,58 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.24439918224016</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.01071388490788548</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3615763187408447</v>
+        <v>0.6431419253349304</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.694999999999993</v>
+        <v>57.83949565217392</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03037383177570093</v>
+        <v>0.2289719626168224</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3396226415094339</v>
       </c>
       <c r="N18" t="n">
-        <v>14.07056045532227</v>
+        <v>87.2583441734314</v>
       </c>
       <c r="O18" t="n">
-        <v>1506.00390625</v>
+        <v>26.4375</v>
       </c>
       <c r="P18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.45282769203186</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.454415559768677</v>
+        <v>87.25832319259644</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1650,19 +1684,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.05511810955266911</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>8.672949743567673e-171</v>
       </c>
       <c r="E19" t="n">
-        <v>0.33333620429039</v>
+        <v>0.5145386457443237</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.694999999999993</v>
+        <v>38.94119047619049</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05141727092946605</v>
+        <v>0.07119314436387607</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1670,36 +1704,38 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1095890410958904</v>
       </c>
       <c r="N19" t="n">
-        <v>9.735885143280029</v>
+        <v>125.6786150932312</v>
       </c>
       <c r="O19" t="n">
-        <v>1506.00390625</v>
+        <v>24.109375</v>
       </c>
       <c r="P19" t="n">
-        <v>10.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.493953704833984</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.495516777038574</v>
+        <v>125.6785950660706</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1715,56 +1751,58 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.008032128120514206</v>
+        <v>0.1379310318135553</v>
       </c>
       <c r="D20" t="n">
-        <v>1.21304235279905e-268</v>
+        <v>1.397268656437835e-80</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3513511121273041</v>
+        <v>0.5976909995079041</v>
       </c>
       <c r="F20" t="n">
-        <v>-6.694999999999993</v>
+        <v>53.29755255255256</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05535841022001419</v>
+        <v>0.2306600425833925</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L20" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.1823899371069182</v>
       </c>
       <c r="N20" t="n">
-        <v>11.53684520721436</v>
+        <v>61.35710883140564</v>
       </c>
       <c r="O20" t="n">
-        <v>1506.23828125</v>
+        <v>24.15625</v>
       </c>
       <c r="P20" t="n">
-        <v>8.9</v>
+        <v>5.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.498727798461914</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.500492572784424</v>
+        <v>61.35707783699036</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -1780,44 +1818,46 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.1734417302108534</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>6.307314793855258e-79</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3501014113426208</v>
+        <v>0.5835224390029907</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.694999999999993</v>
+        <v>43.42000000000002</v>
       </c>
       <c r="G21" t="n">
-        <v>0.04419263456090652</v>
+        <v>0.4464589235127479</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.375</v>
+      </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L21" t="n">
-        <v>0.25</v>
+        <v>0.51</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01408450704225352</v>
+        <v>0.2909090909090909</v>
       </c>
       <c r="N21" t="n">
-        <v>13.09890460968018</v>
+        <v>2538.310411214828</v>
       </c>
       <c r="O21" t="n">
-        <v>1509.13671875</v>
+        <v>50.5625</v>
       </c>
       <c r="P21" t="n">
-        <v>9.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q21" t="n">
         <v>4</v>
@@ -1826,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.710393190383911</v>
+        <v>3.422324895858765</v>
       </c>
       <c r="T21" t="n">
-        <v>1.712727069854736</v>
+        <v>2359.284959077835</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -1845,44 +1885,46 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.2941176420843338</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.03063005414254655</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3600354492664337</v>
+        <v>0.6253650188446045</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.694999999999993</v>
+        <v>35.56131779100531</v>
       </c>
       <c r="G22" t="n">
-        <v>0.04727272727272727</v>
+        <v>1.073333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.75</v>
       </c>
       <c r="N22" t="n">
-        <v>10.24337339401245</v>
+        <v>342.8620727062225</v>
       </c>
       <c r="O22" t="n">
-        <v>1509.13671875</v>
+        <v>39.4375</v>
       </c>
       <c r="P22" t="n">
-        <v>9.300000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
@@ -1891,10 +1933,10 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.445538997650146</v>
+        <v>2.591594934463501</v>
       </c>
       <c r="T22" t="n">
-        <v>1.447184562683105</v>
+        <v>150.192587852478</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -1910,44 +1952,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.005847952928251443</v>
+        <v>0.08719345898922705</v>
       </c>
       <c r="D23" t="n">
-        <v>1.811128572821972e-307</v>
+        <v>8.424760656613393e-13</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3535859286785126</v>
+        <v>0.5638859272003174</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.694999999999993</v>
+        <v>20.78005882352943</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0358291226458429</v>
+        <v>0.112540192926045</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.25</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1346153846153846</v>
       </c>
       <c r="N23" t="n">
-        <v>10.06352853775024</v>
+        <v>181.7903079986572</v>
       </c>
       <c r="O23" t="n">
-        <v>1509.13671875</v>
+        <v>38.328125</v>
       </c>
       <c r="P23" t="n">
-        <v>10.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q23" t="n">
         <v>4</v>
@@ -1956,10 +2000,10 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.51862096786499</v>
+        <v>3.106200695037842</v>
       </c>
       <c r="T23" t="n">
-        <v>1.52019739151001</v>
+        <v>110.0732898712158</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -1975,19 +2019,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.1746031717208365</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>3.609335106029891e-158</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3177126049995422</v>
+        <v>0.495968759059906</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.694999999999993</v>
+        <v>77.67072463768118</v>
       </c>
       <c r="G24" t="n">
-        <v>0.119815668202765</v>
+        <v>0.2365591397849462</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1995,36 +2039,38 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L24" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="N24" t="n">
-        <v>10.42429184913635</v>
+        <v>31.87324810028076</v>
       </c>
       <c r="O24" t="n">
-        <v>1509.13671875</v>
+        <v>47.546875</v>
       </c>
       <c r="P24" t="n">
-        <v>10.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.447219848632812</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.448699235916138</v>
+        <v>31.8732430934906</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2040,56 +2086,58 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.2013422782144949</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1.058797756759345e-155</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3314136564731598</v>
+        <v>0.5474245548248291</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.694999999999993</v>
+        <v>32.18078947368423</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.3785822021116139</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="N25" t="n">
-        <v>3.062867879867554</v>
+        <v>29.39018201828003</v>
       </c>
       <c r="O25" t="n">
-        <v>1509.13671875</v>
+        <v>48</v>
       </c>
       <c r="P25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q25" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>4</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.54695725440979</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.548557281494141</v>
+        <v>29.3901789188385</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2105,19 +2153,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.1428571402822066</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>5.42286353767171e-159</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3261704742908478</v>
+        <v>0.4237134456634521</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.694999999999993</v>
+        <v>24.03102941176473</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1351819757365685</v>
+        <v>0.2547660311958406</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2125,36 +2173,38 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
       <c r="K26" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="L26" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1025641025641026</v>
       </c>
       <c r="N26" t="n">
-        <v>2.11370062828064</v>
+        <v>30.50363492965698</v>
       </c>
       <c r="O26" t="n">
-        <v>1509.13671875</v>
+        <v>48.234375</v>
       </c>
       <c r="P26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.361691474914551</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.363716602325439</v>
+        <v>30.5036301612854</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2170,56 +2220,58 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.2359550520912764</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>6.325060334079257e-156</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3252985775470734</v>
+        <v>0.5793122053146362</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.694999999999993</v>
+        <v>44.25500000000002</v>
       </c>
       <c r="G27" t="n">
-        <v>0.106703146374829</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1891891891891892</v>
       </c>
       <c r="N27" t="n">
-        <v>3.139597177505493</v>
+        <v>26.62699007987976</v>
       </c>
       <c r="O27" t="n">
-        <v>1509.13671875</v>
+        <v>48.375</v>
       </c>
       <c r="P27" t="n">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.386247634887695</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.388109683990479</v>
+        <v>26.62698698043823</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2235,56 +2287,58 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.1923076883144314</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>2.438031653153288e-156</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3308320045471191</v>
+        <v>0.5616746544837952</v>
       </c>
       <c r="F28" t="n">
-        <v>-6.694999999999993</v>
+        <v>50.60811111111113</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1181818181818182</v>
+        <v>0.4212121212121212</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1954022988505747</v>
       </c>
       <c r="N28" t="n">
-        <v>2.272003173828125</v>
+        <v>29.33649182319641</v>
       </c>
       <c r="O28" t="n">
-        <v>1509.13671875</v>
+        <v>49.6875</v>
       </c>
       <c r="P28" t="n">
-        <v>12.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.368595600128174</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.370246648788452</v>
+        <v>29.33648705482483</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -2300,56 +2354,58 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.1391304319092628</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2.249050944985316e-158</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3268276154994965</v>
+        <v>0.4437164664268494</v>
       </c>
       <c r="F29" t="n">
-        <v>-6.694999999999993</v>
+        <v>43.55833333333334</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1354166666666667</v>
+        <v>0.2690972222222222</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
       <c r="K29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="N29" t="n">
-        <v>1.895581007003784</v>
+        <v>30.93264412879944</v>
       </c>
       <c r="O29" t="n">
-        <v>1509.13671875</v>
+        <v>49.46875</v>
       </c>
       <c r="P29" t="n">
-        <v>3.1</v>
+        <v>14.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.397442579269409</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.39905834197998</v>
+        <v>30.93264102935791</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2365,44 +2421,46 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.1351351329985391</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2.244535351910224e-155</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4468841254711151</v>
+        <v>0.4958815574645996</v>
       </c>
       <c r="F30" t="n">
-        <v>-6.694999999999993</v>
+        <v>45.98723076923079</v>
       </c>
       <c r="G30" t="n">
-        <v>0.78</v>
+        <v>3.68</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0.25</v>
+        <v>0.4528301886792453</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1379310344827586</v>
       </c>
       <c r="N30" t="n">
-        <v>11.87508130073547</v>
+        <v>93.63500499725342</v>
       </c>
       <c r="O30" t="n">
-        <v>1509.13671875</v>
+        <v>83.15625</v>
       </c>
       <c r="P30" t="n">
-        <v>10.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q30" t="n">
         <v>4</v>
@@ -2411,10 +2469,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.419911623001099</v>
+        <v>3.022176027297974</v>
       </c>
       <c r="T30" t="n">
-        <v>1.421907186508179</v>
+        <v>45.48308300971985</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -2430,44 +2488,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.1194029827489419</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1.781009471778631e-155</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4375941157341003</v>
+        <v>0.4875025153160095</v>
       </c>
       <c r="F31" t="n">
-        <v>-6.694999999999993</v>
+        <v>49.3340305084746</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7572815533980582</v>
+        <v>4.368932038834951</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.25</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="M31" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.239766081871345</v>
       </c>
       <c r="N31" t="n">
-        <v>3.4451584815979</v>
+        <v>105.1430802345276</v>
       </c>
       <c r="O31" t="n">
-        <v>1509.13671875</v>
+        <v>89.9375</v>
       </c>
       <c r="P31" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
         <v>4</v>
@@ -2476,10 +2536,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.559489488601685</v>
+        <v>2.659034967422485</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5610191822052</v>
+        <v>52.74488711357117</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -2495,56 +2555,58 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.109589038934134</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>2.083664844636364e-155</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4345121085643768</v>
+        <v>0.4611914157867432</v>
       </c>
       <c r="F32" t="n">
-        <v>-6.694999999999993</v>
+        <v>43.80226495726498</v>
       </c>
       <c r="G32" t="n">
-        <v>0.78</v>
+        <v>4.04</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.186046511627907</v>
       </c>
       <c r="N32" t="n">
-        <v>1.575536727905273</v>
+        <v>52.87909507751465</v>
       </c>
       <c r="O32" t="n">
-        <v>1509.13671875</v>
+        <v>90.359375</v>
       </c>
       <c r="P32" t="n">
-        <v>7.3</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.3248918056488037</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0.3264880180358887</v>
+        <v>52.87908887863159</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -2560,56 +2622,58 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.331034478120333</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>5.556490054616226e-79</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4005701541900635</v>
+        <v>0.6410205960273743</v>
       </c>
       <c r="F33" t="n">
-        <v>-6.694999999999993</v>
+        <v>70.02869718309861</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2160664819944598</v>
+        <v>1.861495844875346</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
       <c r="K33" t="n">
         <v>0.5</v>
       </c>
       <c r="L33" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.4857142857142858</v>
       </c>
       <c r="N33" t="n">
-        <v>10.21217250823975</v>
+        <v>73.89662909507751</v>
       </c>
       <c r="O33" t="n">
-        <v>1509.13671875</v>
+        <v>89.65625</v>
       </c>
       <c r="P33" t="n">
-        <v>11.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3448114395141602</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3465657234191895</v>
+        <v>73.8966269493103</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -2625,56 +2689,58 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.233333328817284</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>2.407401295684917e-155</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3832495212554932</v>
+        <v>0.6021385788917542</v>
       </c>
       <c r="F34" t="n">
-        <v>-6.694999999999993</v>
+        <v>56.239717920354</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1133720930232558</v>
+        <v>0.625</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
       <c r="K34" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="N34" t="n">
-        <v>13.8501513004303</v>
+        <v>41.59338092803955</v>
       </c>
       <c r="O34" t="n">
-        <v>1509.13671875</v>
+        <v>37.1875</v>
       </c>
       <c r="P34" t="n">
-        <v>10.1</v>
+        <v>14.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.452259540557861</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1.453809261322021</v>
+        <v>41.59333992004395</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -2690,44 +2756,46 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.2721088391630803</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.03134301059563741</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3523319959640503</v>
+        <v>0.6418632864952087</v>
       </c>
       <c r="F35" t="n">
-        <v>-6.694999999999993</v>
+        <v>25.04384615384615</v>
       </c>
       <c r="G35" t="n">
-        <v>0.06830122591943957</v>
+        <v>0.4649737302977233</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5</v>
+        <v>0.6212121212121212</v>
       </c>
       <c r="M35" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3121693121693122</v>
       </c>
       <c r="N35" t="n">
-        <v>11.57649636268616</v>
+        <v>140.1787841320038</v>
       </c>
       <c r="O35" t="n">
-        <v>1509.13671875</v>
+        <v>38.421875</v>
       </c>
       <c r="P35" t="n">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q35" t="n">
         <v>4</v>
@@ -2736,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.21482253074646</v>
+        <v>2.880224943161011</v>
       </c>
       <c r="T35" t="n">
-        <v>1.216347694396973</v>
+        <v>70.03197503089905</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -2755,44 +2823,46 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.1851851812856272</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.08901085364869357</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3204767107963562</v>
+        <v>0.7136691808700562</v>
       </c>
       <c r="F36" t="n">
-        <v>-6.694999999999993</v>
+        <v>16.084657480315</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1236133122028526</v>
+        <v>0.4659270998415214</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="L36" t="n">
-        <v>0.25</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="M36" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2366412213740458</v>
       </c>
       <c r="N36" t="n">
-        <v>9.967308044433594</v>
+        <v>117.9811089038849</v>
       </c>
       <c r="O36" t="n">
-        <v>1509.140625</v>
+        <v>85.140625</v>
       </c>
       <c r="P36" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="Q36" t="n">
         <v>4</v>
@@ -2801,10 +2871,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.460657119750977</v>
+        <v>3.463802814483643</v>
       </c>
       <c r="T36" t="n">
-        <v>1.462340354919434</v>
+        <v>52.61568570137024</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -2820,44 +2890,46 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.1254901913282586</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>5.292344692655624e-232</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3582548201084137</v>
+        <v>0.5988379120826721</v>
       </c>
       <c r="F37" t="n">
-        <v>-6.694999999999993</v>
+        <v>81.12424089068827</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08271474019088017</v>
+        <v>0.6436903499469777</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
       <c r="K37" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L37" t="n">
-        <v>0.25</v>
+        <v>0.4714285714285714</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.4039735099337748</v>
       </c>
       <c r="N37" t="n">
-        <v>3.299293518066406</v>
+        <v>136.8003759384155</v>
       </c>
       <c r="O37" t="n">
-        <v>1509.24609375</v>
+        <v>88.25</v>
       </c>
       <c r="P37" t="n">
-        <v>9.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q37" t="n">
         <v>4</v>
@@ -2866,10 +2938,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.457995653152466</v>
+        <v>2.602930784225464</v>
       </c>
       <c r="T37" t="n">
-        <v>1.459661722183228</v>
+        <v>50.02520799636841</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -2885,56 +2957,58 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.2626262580553005</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.03216663672496465</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3565259277820587</v>
+        <v>0.5355229377746582</v>
       </c>
       <c r="F38" t="n">
-        <v>-6.694999999999993</v>
+        <v>36.9065384615385</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1009055627425614</v>
+        <v>0.5963777490297542</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
       <c r="K38" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1946308724832215</v>
       </c>
       <c r="N38" t="n">
-        <v>1.042274236679077</v>
+        <v>73.05420994758606</v>
       </c>
       <c r="O38" t="n">
-        <v>1509.359375</v>
+        <v>37.625</v>
       </c>
       <c r="P38" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.3469047546386719</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0.3484566211700439</v>
+        <v>73.05417704582214</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -2950,19 +3024,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.1944444408371914</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>5.019806190416597e-233</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3533079922199249</v>
+        <v>0.5569300055503845</v>
       </c>
       <c r="F39" t="n">
-        <v>-6.694999999999993</v>
+        <v>62.34923076923079</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1150442477876106</v>
+        <v>0.336283185840708</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2970,36 +3044,38 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L39" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.07514450867052024</v>
       </c>
       <c r="N39" t="n">
-        <v>1.716034650802612</v>
+        <v>57.43383383750916</v>
       </c>
       <c r="O39" t="n">
-        <v>1509.4296875</v>
+        <v>42.515625</v>
       </c>
       <c r="P39" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.453843355178833</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0.4555583000183105</v>
+        <v>57.43382906913757</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -3015,44 +3091,46 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.1111111086395062</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>3.31009421283509e-157</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2973054349422455</v>
+        <v>0.6540348529815674</v>
       </c>
       <c r="F40" t="n">
-        <v>-6.694999999999993</v>
+        <v>49.74600358422941</v>
       </c>
       <c r="G40" t="n">
-        <v>0.08590308370044053</v>
+        <v>0.25</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
       <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
         <v>0.5</v>
       </c>
-      <c r="L40" t="n">
-        <v>0.25</v>
-      </c>
       <c r="M40" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="N40" t="n">
-        <v>10.85743951797485</v>
+        <v>95.51131868362427</v>
       </c>
       <c r="O40" t="n">
-        <v>1509.8046875</v>
+        <v>31.375</v>
       </c>
       <c r="P40" t="n">
-        <v>11.3</v>
+        <v>9</v>
       </c>
       <c r="Q40" t="n">
         <v>4</v>
@@ -3061,10 +3139,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.3169059753417969</v>
+        <v>2.995203733444214</v>
       </c>
       <c r="T40" t="n">
-        <v>0.3184688091278076</v>
+        <v>43.28196573257446</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -3080,44 +3158,46 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.1151079120915067</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>2.503385863140841e-85</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2983242273330688</v>
+        <v>0.625676691532135</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.694999999999993</v>
+        <v>61.69963636363636</v>
       </c>
       <c r="G41" t="n">
-        <v>0.05349794238683128</v>
+        <v>0.139917695473251</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L41" t="n">
-        <v>0.25</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="N41" t="n">
-        <v>3.430304288864136</v>
+        <v>80.5112829208374</v>
       </c>
       <c r="O41" t="n">
-        <v>1509.80859375</v>
+        <v>27.6875</v>
       </c>
       <c r="P41" t="n">
-        <v>5.3</v>
+        <v>15.5</v>
       </c>
       <c r="Q41" t="n">
         <v>4</v>
@@ -3126,10 +3206,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.552063941955566</v>
+        <v>3.091278076171875</v>
       </c>
       <c r="T41" t="n">
-        <v>1.553599834442139</v>
+        <v>37.34941697120667</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3145,44 +3225,46 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01273885288652687</v>
+        <v>0.1005586566561594</v>
       </c>
       <c r="D42" t="n">
-        <v>7.842246496009318e-255</v>
+        <v>1.22342463423494e-234</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3304620385169983</v>
+        <v>0.5203850269317627</v>
       </c>
       <c r="F42" t="n">
-        <v>-6.694999999999993</v>
+        <v>46.14681818181819</v>
       </c>
       <c r="G42" t="n">
-        <v>0.08914285714285715</v>
+        <v>0.2434285714285714</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L42" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="N42" t="n">
-        <v>7.940751791000366</v>
+        <v>94.10230398178101</v>
       </c>
       <c r="O42" t="n">
-        <v>1509.80859375</v>
+        <v>38.78125</v>
       </c>
       <c r="P42" t="n">
-        <v>12.1</v>
+        <v>15.4</v>
       </c>
       <c r="Q42" t="n">
         <v>4</v>
@@ -3191,10 +3273,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.3915088176727295</v>
+        <v>2.612574815750122</v>
       </c>
       <c r="T42" t="n">
-        <v>0.3939275741577148</v>
+        <v>40.97972989082336</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -3210,56 +3292,58 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.2468354380668163</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>4.012739307999906e-155</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3637755811214447</v>
+        <v>0.6392710208892822</v>
       </c>
       <c r="F43" t="n">
-        <v>-6.694999999999993</v>
+        <v>48.21031732418527</v>
       </c>
       <c r="G43" t="n">
-        <v>0.07228915662650602</v>
+        <v>0.9351251158480074</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
       <c r="K43" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.02564102564102564</v>
+        <v>0.4160583941605839</v>
       </c>
       <c r="N43" t="n">
-        <v>12.52107214927673</v>
+        <v>121.0973088741302</v>
       </c>
       <c r="O43" t="n">
-        <v>1509.984375</v>
+        <v>34.78125</v>
       </c>
       <c r="P43" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.446927785873413</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>1.448587656021118</v>
+        <v>121.0972499847412</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3275,44 +3359,46 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.1415929164127967</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>6.709237460203354e-79</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3320682942867279</v>
+        <v>0.6393852829933167</v>
       </c>
       <c r="F44" t="n">
-        <v>-6.694999999999993</v>
+        <v>-7.318215384615371</v>
       </c>
       <c r="G44" t="n">
-        <v>0.08955223880597014</v>
+        <v>0.5304247990815155</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.25</v>
+        <v>0.3859649122807017</v>
       </c>
       <c r="M44" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3311036789297659</v>
       </c>
       <c r="N44" t="n">
-        <v>10.58960342407227</v>
+        <v>149.4924519062042</v>
       </c>
       <c r="O44" t="n">
-        <v>1510.25390625</v>
+        <v>40.09375</v>
       </c>
       <c r="P44" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="Q44" t="n">
         <v>4</v>
@@ -3321,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.522054433822632</v>
+        <v>3.727458000183105</v>
       </c>
       <c r="T44" t="n">
-        <v>1.523772478103638</v>
+        <v>52.33642387390137</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -3340,56 +3426,58 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.3083700403510429</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>0.03261355567381161</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3620854616165161</v>
+        <v>0.6349319219589233</v>
       </c>
       <c r="F45" t="n">
-        <v>-6.694999999999993</v>
+        <v>49.43543628808865</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02138744173293118</v>
+        <v>0.3745544282972306</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
       <c r="K45" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.6604938271604939</v>
       </c>
       <c r="N45" t="n">
-        <v>11.24179005622864</v>
+        <v>109.82266497612</v>
       </c>
       <c r="O45" t="n">
-        <v>1510.83203125</v>
+        <v>35.140625</v>
       </c>
       <c r="P45" t="n">
-        <v>10.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.56652569770813</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>1.568768978118896</v>
+        <v>109.8225989341736</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -3405,56 +3493,58 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.2337278075443787</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>0.01484983994858796</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3481395244598389</v>
+        <v>0.6115736365318298</v>
       </c>
       <c r="F46" t="n">
-        <v>-6.694999999999993</v>
+        <v>56.87479856015509</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02160066463583495</v>
+        <v>0.2650235391858211</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
       <c r="K46" t="n">
         <v>0.5</v>
       </c>
       <c r="L46" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="N46" t="n">
-        <v>4.401284456253052</v>
+        <v>100.7978947162628</v>
       </c>
       <c r="O46" t="n">
-        <v>1510.83203125</v>
+        <v>35.21875</v>
       </c>
       <c r="P46" t="n">
-        <v>11.3</v>
+        <v>5.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.489950180053711</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1.492054462432861</v>
+        <v>100.7978558540344</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -3470,56 +3560,58 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.2773109211246558</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.001247994874258283</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3639097213745117</v>
+        <v>0.6308389902114868</v>
       </c>
       <c r="F47" t="n">
-        <v>-6.694999999999993</v>
+        <v>21.57368421052632</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0310880829015544</v>
+        <v>0.2351534475886808</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
       <c r="K47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2792792792792793</v>
       </c>
       <c r="N47" t="n">
-        <v>9.897516250610352</v>
+        <v>87.02002286911011</v>
       </c>
       <c r="O47" t="n">
-        <v>1510.89453125</v>
+        <v>44.96875</v>
       </c>
       <c r="P47" t="n">
-        <v>9.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.3515493869781494</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0.3532202243804932</v>
+        <v>87.02001690864563</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -3535,56 +3627,58 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2115384576035503</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1.650703816886613e-155</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3680242300033569</v>
+        <v>0.5837224125862122</v>
       </c>
       <c r="F48" t="n">
-        <v>-6.694999999999993</v>
+        <v>40.48416666666668</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1670235546038544</v>
+        <v>0.5053533190578159</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
       <c r="K48" t="n">
         <v>0.5</v>
       </c>
       <c r="L48" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2452830188679246</v>
       </c>
       <c r="N48" t="n">
-        <v>9.118991136550903</v>
+        <v>67.3652331829071</v>
       </c>
       <c r="O48" t="n">
-        <v>1510.89453125</v>
+        <v>40.03125</v>
       </c>
       <c r="P48" t="n">
-        <v>10.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.50508451461792</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>1.506625652313232</v>
+        <v>67.36517119407654</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -3600,56 +3694,58 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1523809496671202</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>2.943114372540767e-79</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3522202372550964</v>
+        <v>0.5638047456741333</v>
       </c>
       <c r="F49" t="n">
-        <v>-6.694999999999993</v>
+        <v>73.89631578947372</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1502890173410405</v>
+        <v>0.3429672447013488</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L49" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1869918699186992</v>
       </c>
       <c r="N49" t="n">
-        <v>13.59402275085449</v>
+        <v>40.94291424751282</v>
       </c>
       <c r="O49" t="n">
-        <v>1510.89453125</v>
+        <v>34.40625</v>
       </c>
       <c r="P49" t="n">
-        <v>10.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1.445708274841309</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>1.447296619415283</v>
+        <v>40.94286298751831</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -3665,56 +3761,58 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.1911764660207614</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>0.03147446394118519</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3514077365398407</v>
+        <v>0.5948474407196045</v>
       </c>
       <c r="F50" t="n">
-        <v>-6.694999999999993</v>
+        <v>62.39579243765084</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1494252873563219</v>
+        <v>0.6609195402298851</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
       <c r="K50" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2805755395683453</v>
       </c>
       <c r="N50" t="n">
-        <v>9.183413505554199</v>
+        <v>68.04189300537109</v>
       </c>
       <c r="O50" t="n">
-        <v>1511.1328125</v>
+        <v>19.734375</v>
       </c>
       <c r="P50" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="Q50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1.43329644203186</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>1.434942245483398</v>
+        <v>68.04185700416565</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -3730,44 +3828,46 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.1585365816158537</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1.264024049723077e-155</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3513664901256561</v>
+        <v>0.5793190002441406</v>
       </c>
       <c r="F51" t="n">
-        <v>-6.694999999999993</v>
+        <v>11.9230913978495</v>
       </c>
       <c r="G51" t="n">
-        <v>0.103861517976032</v>
+        <v>0.4167776298268975</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.25</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="M51" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.3710691823899371</v>
       </c>
       <c r="N51" t="n">
-        <v>13.14925694465637</v>
+        <v>149.0001132488251</v>
       </c>
       <c r="O51" t="n">
-        <v>1511.46484375</v>
+        <v>19.5</v>
       </c>
       <c r="P51" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q51" t="n">
         <v>4</v>
@@ -3776,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>1.531296491622925</v>
+        <v>3.00985312461853</v>
       </c>
       <c r="T51" t="n">
-        <v>1.532980442047119</v>
+        <v>60.81364107131958</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -3795,56 +3895,58 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.008403360933196829</v>
+        <v>0.2078651640166962</v>
       </c>
       <c r="D52" t="n">
-        <v>2.960553565183628e-265</v>
+        <v>3.811146423519126e-155</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3619620203971863</v>
+        <v>0.5970848798751831</v>
       </c>
       <c r="F52" t="n">
-        <v>-6.694999999999993</v>
+        <v>46.06334848484849</v>
       </c>
       <c r="G52" t="n">
-        <v>0.05656272661348803</v>
+        <v>0.5351704133430022</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
       <c r="K52" t="n">
-        <v>0.75</v>
+        <v>0.87</v>
       </c>
       <c r="L52" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.5024875621890548</v>
       </c>
       <c r="N52" t="n">
-        <v>11.57462024688721</v>
+        <v>116.0841212272644</v>
       </c>
       <c r="O52" t="n">
-        <v>1511.46484375</v>
+        <v>21.875</v>
       </c>
       <c r="P52" t="n">
-        <v>10.3</v>
+        <v>5</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1.464968919754028</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>1.466602563858032</v>
+        <v>116.0840501785278</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -3860,56 +3962,58 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.1415384596650414</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>8.700512584883141e-05</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3393140435218811</v>
+        <v>0.6485660076141357</v>
       </c>
       <c r="F53" t="n">
-        <v>-6.694999999999993</v>
+        <v>41.75385167464117</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0416221985058698</v>
+        <v>0.1339381003201708</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
       <c r="K53" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.1121495327102804</v>
       </c>
       <c r="N53" t="n">
-        <v>11.58727788925171</v>
+        <v>109.3119170665741</v>
       </c>
       <c r="O53" t="n">
-        <v>1511.93359375</v>
+        <v>20.421875</v>
       </c>
       <c r="P53" t="n">
-        <v>9.300000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.522054672241211</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>1.523861885070801</v>
+        <v>109.3118767738342</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -3925,56 +4029,58 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.1744966400792758</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>5.120040658383118e-80</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3256970345973969</v>
+        <v>0.6241183876991272</v>
       </c>
       <c r="F54" t="n">
-        <v>-6.694999999999993</v>
+        <v>-9.829369565217377</v>
       </c>
       <c r="G54" t="n">
-        <v>0.05739514348785872</v>
+        <v>0.4753495217071376</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="N54" t="n">
-        <v>11.22345447540283</v>
+        <v>229.9391770362854</v>
       </c>
       <c r="O54" t="n">
-        <v>1511.9375</v>
+        <v>20.8125</v>
       </c>
       <c r="P54" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1.452330112457275</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>1.454082727432251</v>
+        <v>229.9391229152679</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -3990,56 +4096,58 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.1865671620196592</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>2.356233700818133e-06</v>
       </c>
       <c r="E55" t="n">
-        <v>0.343548446893692</v>
+        <v>0.6216738820075989</v>
       </c>
       <c r="F55" t="n">
-        <v>-6.694999999999993</v>
+        <v>24.22750000000002</v>
       </c>
       <c r="G55" t="n">
-        <v>0.05045278137128072</v>
+        <v>0.1552393272962484</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
       <c r="K55" t="n">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1397849462365592</v>
       </c>
       <c r="N55" t="n">
-        <v>3.621444463729858</v>
+        <v>71.94218492507935</v>
       </c>
       <c r="O55" t="n">
-        <v>1511.94140625</v>
+        <v>20.484375</v>
       </c>
       <c r="P55" t="n">
-        <v>13.1</v>
+        <v>5.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>1.520708799362183</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>1.522382974624634</v>
+        <v>71.94211673736572</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -4055,44 +4163,46 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.1447368390997231</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>5.328094693801895e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>0.3342143893241882</v>
+        <v>0.5665460824966431</v>
       </c>
       <c r="F56" t="n">
-        <v>-6.694999999999993</v>
+        <v>39.12070850202431</v>
       </c>
       <c r="G56" t="n">
-        <v>0.04977664326738992</v>
+        <v>0.2335673261008296</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L56" t="n">
-        <v>0.25</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="N56" t="n">
-        <v>12.05659079551697</v>
+        <v>171.5674619674683</v>
       </c>
       <c r="O56" t="n">
-        <v>1511.94921875</v>
+        <v>20.859375</v>
       </c>
       <c r="P56" t="n">
-        <v>10.7</v>
+        <v>7.3</v>
       </c>
       <c r="Q56" t="n">
         <v>4</v>
@@ -4101,10 +4211,10 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.3717708587646484</v>
+        <v>3.290996074676514</v>
       </c>
       <c r="T56" t="n">
-        <v>0.3734982013702393</v>
+        <v>81.51416897773743</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -4120,56 +4230,58 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>0.2269503513844877</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>0.007178738932603332</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3695140182971954</v>
+        <v>0.5896973609924316</v>
       </c>
       <c r="F57" t="n">
-        <v>-6.694999999999993</v>
+        <v>52.94386093461776</v>
       </c>
       <c r="G57" t="n">
-        <v>0.02687801516195727</v>
+        <v>0.2639558924879393</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
       <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.04</v>
+        <v>0.2913385826771653</v>
       </c>
       <c r="N57" t="n">
-        <v>10.68418478965759</v>
+        <v>93.42482709884644</v>
       </c>
       <c r="O57" t="n">
-        <v>1514.32421875</v>
+        <v>20.734375</v>
       </c>
       <c r="P57" t="n">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>1.628901481628418</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>1.630803346633911</v>
+        <v>93.42480516433716</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -4185,44 +4297,46 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.0120481921868196</v>
+        <v>0.2145593822462971</v>
       </c>
       <c r="D58" t="n">
-        <v>3.542014107114671e-257</v>
+        <v>3.760073892041286e-155</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3487640619277954</v>
+        <v>0.6613680124282837</v>
       </c>
       <c r="F58" t="n">
-        <v>-6.694999999999993</v>
+        <v>47.53226005513096</v>
       </c>
       <c r="G58" t="n">
-        <v>0.08423326133909287</v>
+        <v>0.6987041036717062</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
       <c r="K58" t="n">
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>0.25</v>
+        <v>0.475609756097561</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="N58" t="n">
-        <v>10.82381558418274</v>
+        <v>204.0498929023743</v>
       </c>
       <c r="O58" t="n">
-        <v>1514.32421875</v>
+        <v>19.9375</v>
       </c>
       <c r="P58" t="n">
-        <v>10.1</v>
+        <v>8.9</v>
       </c>
       <c r="Q58" t="n">
         <v>4</v>
@@ -4231,10 +4345,10 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>1.628249645233154</v>
+        <v>3.308865070343018</v>
       </c>
       <c r="T58" t="n">
-        <v>1.630011796951294</v>
+        <v>107.5027179718018</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -4250,56 +4364,58 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>0.315789468690849</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>7.549254288381402e-79</v>
       </c>
       <c r="E59" t="n">
-        <v>0.359289288520813</v>
+        <v>0.6473841071128845</v>
       </c>
       <c r="F59" t="n">
-        <v>-6.694999999999993</v>
+        <v>37.85146137677353</v>
       </c>
       <c r="G59" t="n">
-        <v>0.09848484848484848</v>
+        <v>1.136363636363636</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.6296296296296295</v>
       </c>
       <c r="N59" t="n">
-        <v>10.40878295898438</v>
+        <v>95.01514601707458</v>
       </c>
       <c r="O59" t="n">
-        <v>1514.32421875</v>
+        <v>20.8125</v>
       </c>
       <c r="P59" t="n">
-        <v>10.4</v>
+        <v>13.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>1.457972526550293</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>1.460432767868042</v>
+        <v>95.01511788368225</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -4315,56 +4431,58 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.00446428549356267</v>
+        <v>0.1285140542600119</v>
       </c>
       <c r="D60" t="n">
-        <v>8.265132997605698e-314</v>
+        <v>1.889803135917405e-158</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3573783934116364</v>
+        <v>0.5116021633148193</v>
       </c>
       <c r="F60" t="n">
-        <v>-6.694999999999993</v>
+        <v>12.21455188679249</v>
       </c>
       <c r="G60" t="n">
-        <v>0.02725366876310273</v>
+        <v>0.129979035639413</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1970802919708029</v>
       </c>
       <c r="N60" t="n">
-        <v>14.37377834320068</v>
+        <v>109.1969590187073</v>
       </c>
       <c r="O60" t="n">
-        <v>1514.32421875</v>
+        <v>19.859375</v>
       </c>
       <c r="P60" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>1.486737489700317</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>1.48843240737915</v>
+        <v>109.1969089508057</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -4380,56 +4498,58 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>0.2499999959781805</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>7.751579743209176e-79</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3793801069259644</v>
+        <v>0.5810978412628174</v>
       </c>
       <c r="F61" t="n">
-        <v>-6.694999999999993</v>
+        <v>40.87333333333336</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3157894736842105</v>
+        <v>2.214574898785425</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
       <c r="K61" t="n">
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.4146341463414633</v>
       </c>
       <c r="N61" t="n">
-        <v>10.56781244277954</v>
+        <v>105.5565929412842</v>
       </c>
       <c r="O61" t="n">
-        <v>1514.32421875</v>
+        <v>20.671875</v>
       </c>
       <c r="P61" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>1.48133373260498</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>1.482977867126465</v>
+        <v>105.5565619468689</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -4445,56 +4565,58 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>0.1666666630230035</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>1.82771932340829e-156</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3254241049289703</v>
+        <v>0.4752743244171143</v>
       </c>
       <c r="F62" t="n">
-        <v>-6.694999999999993</v>
+        <v>48.63550000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>0.195</v>
+        <v>0.4275</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
       <c r="K62" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="N62" t="n">
-        <v>3.619588851928711</v>
+        <v>31.90827894210815</v>
       </c>
       <c r="O62" t="n">
-        <v>1514.32421875</v>
+        <v>26.796875</v>
       </c>
       <c r="P62" t="n">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>1.437713384628296</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>1.439305305480957</v>
+        <v>31.90825986862183</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -4510,19 +4632,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>0.06896551572318671</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>2.291493039758307e-239</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3176030814647675</v>
+        <v>0.4284061789512634</v>
       </c>
       <c r="F63" t="n">
-        <v>-6.694999999999993</v>
+        <v>50.56057692307695</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1087866108786611</v>
+        <v>0.1743375174337518</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -4530,36 +4652,38 @@
       <c r="I63" t="n">
         <v>0</v>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
       <c r="K63" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07216494845360824</v>
       </c>
       <c r="N63" t="n">
-        <v>8.809430599212646</v>
+        <v>52.95605301856995</v>
       </c>
       <c r="O63" t="n">
-        <v>1514.32421875</v>
+        <v>21.828125</v>
       </c>
       <c r="P63" t="n">
-        <v>11.8</v>
+        <v>5.3</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.3265001773834229</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.3280789852142334</v>
+        <v>52.95597910881042</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -4575,44 +4699,46 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>0.181818178267886</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1.027963793723237e-155</v>
       </c>
       <c r="E64" t="n">
-        <v>0.3184672594070435</v>
+        <v>0.5958529114723206</v>
       </c>
       <c r="F64" t="n">
-        <v>-6.694999999999993</v>
+        <v>45.57954545454547</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1278688524590164</v>
+        <v>0.4377049180327869</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.25</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="M64" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2215568862275449</v>
       </c>
       <c r="N64" t="n">
-        <v>9.809545755386353</v>
+        <v>94.91445803642273</v>
       </c>
       <c r="O64" t="n">
-        <v>1514.32421875</v>
+        <v>20.421875</v>
       </c>
       <c r="P64" t="n">
-        <v>10.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q64" t="n">
         <v>4</v>
@@ -4621,10 +4747,10 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>1.435290098190308</v>
+        <v>3.651123762130737</v>
       </c>
       <c r="T64" t="n">
-        <v>1.436878681182861</v>
+        <v>44.7390661239624</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -4640,56 +4766,58 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>0.1592920326008302</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1.644973154223386e-157</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3219119608402252</v>
+        <v>0.4853648841381073</v>
       </c>
       <c r="F65" t="n">
-        <v>-6.694999999999993</v>
+        <v>56.70000000000002</v>
       </c>
       <c r="G65" t="n">
-        <v>0.156312625250501</v>
+        <v>0.2985971943887776</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1025641025641026</v>
       </c>
       <c r="N65" t="n">
-        <v>6.040205478668213</v>
+        <v>49.85166525840759</v>
       </c>
       <c r="O65" t="n">
-        <v>1514.32421875</v>
+        <v>19.84375</v>
       </c>
       <c r="P65" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>1.502256631851196</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>1.50404691696167</v>
+        <v>49.85157608985901</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -4705,56 +4833,58 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>0.1925133656827476</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>3.687106795403599e-156</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3294911682605743</v>
+        <v>0.5733634829521179</v>
       </c>
       <c r="F66" t="n">
-        <v>-6.694999999999993</v>
+        <v>38.49889423076925</v>
       </c>
       <c r="G66" t="n">
-        <v>0.09786700125470514</v>
+        <v>0.4015056461731493</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L66" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="N66" t="n">
-        <v>9.838013410568237</v>
+        <v>40.76638102531433</v>
       </c>
       <c r="O66" t="n">
-        <v>1514.32421875</v>
+        <v>21.796875</v>
       </c>
       <c r="P66" t="n">
-        <v>11.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.3295505046844482</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>0.3311994075775146</v>
+        <v>40.76634287834167</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -4770,56 +4900,58 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>0.2547169763474547</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>9.511776100514363e-79</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3287849128246307</v>
+        <v>0.6278840303421021</v>
       </c>
       <c r="F67" t="n">
-        <v>-6.694999999999993</v>
+        <v>65.05757466281314</v>
       </c>
       <c r="G67" t="n">
-        <v>0.1068493150684932</v>
+        <v>0.7</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
       <c r="K67" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2233009708737864</v>
       </c>
       <c r="N67" t="n">
-        <v>9.913764476776123</v>
+        <v>43.52314376831055</v>
       </c>
       <c r="O67" t="n">
-        <v>1514.32421875</v>
+        <v>20.96875</v>
       </c>
       <c r="P67" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="Q67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>1.479658842086792</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>1.482023239135742</v>
+        <v>43.52306485176086</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -4835,56 +4967,58 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>0.1333333308843538</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1.857009361188231e-155</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4152870178222656</v>
+        <v>0.4196167886257172</v>
       </c>
       <c r="F68" t="n">
-        <v>-6.694999999999993</v>
+        <v>-1.215963600909959</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6141732283464567</v>
+        <v>5.125984251968504</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
       <c r="K68" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0.2</v>
+        <v>0.2553191489361702</v>
       </c>
       <c r="N68" t="n">
-        <v>4.961272954940796</v>
+        <v>57.20432019233704</v>
       </c>
       <c r="O68" t="n">
-        <v>1514.99609375</v>
+        <v>21.390625</v>
       </c>
       <c r="P68" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>1.512712478637695</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>1.514587163925171</v>
+        <v>57.20421242713928</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
